--- a/DateBase/orders/Dang Nguyen48_2026-4-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-15.xlsx
@@ -1076,6 +1076,9 @@
       <c r="G2" t="str">
         <v>01120153532201020101076161026104040423815101552545401411552510154106610103751010555551010104510030302010515101010</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
